--- a/salidas/empresas/UPS.xlsx
+++ b/salidas/empresas/UPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>37.53775024414062</v>
+        <v>37.53774261474609</v>
       </c>
       <c r="C2" t="n">
         <v>74.91000366210938</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>39.97678375244141</v>
+        <v>39.97674942016602</v>
       </c>
       <c r="C4" t="n">
         <v>79.37999725341797</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>40.82788467407227</v>
+        <v>40.8278923034668</v>
       </c>
       <c r="C5" t="n">
         <v>81.06999969482422</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>40.7529182434082</v>
+        <v>40.75290679931641</v>
       </c>
       <c r="C6" t="n">
         <v>80.55000305175781</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>41.65348052978516</v>
+        <v>41.65347671508789</v>
       </c>
       <c r="C7" t="n">
         <v>82.33000183105469</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.86386871337891</v>
+        <v>34.86386108398438</v>
       </c>
       <c r="C8" t="n">
         <v>68.91000366210938</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.62831878662109</v>
+        <v>35.62832641601562</v>
       </c>
       <c r="C9" t="n">
         <v>70.05000305175781</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>36.58960723876953</v>
+        <v>36.58959579467773</v>
       </c>
       <c r="C10" t="n">
         <v>71.94000244140625</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>38.3239631652832</v>
+        <v>38.32397842407227</v>
       </c>
       <c r="C11" t="n">
         <v>75.34999847412109</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>39.8213996887207</v>
+        <v>39.82140350341797</v>
       </c>
       <c r="C12" t="n">
         <v>77.91999816894531</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>38.31889343261719</v>
+        <v>38.31890106201172</v>
       </c>
       <c r="C13" t="n">
         <v>74.98000335693359</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>36.93903350830078</v>
+        <v>36.93904876708984</v>
       </c>
       <c r="C14" t="n">
         <v>72.27999877929688</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>36.07289886474609</v>
+        <v>36.0728874206543</v>
       </c>
       <c r="C15" t="n">
         <v>70.19000244140625</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>36.19623184204102</v>
+        <v>36.19623947143555</v>
       </c>
       <c r="C17" t="n">
         <v>70.43000030517578</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>39.14540100097656</v>
+        <v>39.1453971862793</v>
       </c>
       <c r="C20" t="n">
         <v>75.72000122070312</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>39.21779632568359</v>
+        <v>39.2177848815918</v>
       </c>
       <c r="C21" t="n">
         <v>75.86000061035156</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>39.04245758056641</v>
+        <v>39.0424690246582</v>
       </c>
       <c r="C22" t="n">
         <v>75.09999847412109</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>39.04245758056641</v>
+        <v>39.0424690246582</v>
       </c>
       <c r="C23" t="n">
         <v>75.09999847412109</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>38.52490997314453</v>
+        <v>38.52489852905273</v>
       </c>
       <c r="C24" t="n">
         <v>73.68000030517578</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>36.97721862792969</v>
+        <v>36.97722625732422</v>
       </c>
       <c r="C25" t="n">
         <v>70.72000122070312</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>36.9579963684082</v>
+        <v>36.95800399780273</v>
       </c>
       <c r="C27" t="n">
         <v>70.23999786376953</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>38.42074203491211</v>
+        <v>38.42073440551758</v>
       </c>
       <c r="C28" t="n">
         <v>73.01999664306641</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>38.09976577758789</v>
+        <v>38.09978866577148</v>
       </c>
       <c r="C29" t="n">
         <v>72.41000366210938</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>37.60475158691406</v>
+        <v>37.60475921630859</v>
       </c>
       <c r="C30" t="n">
         <v>71.01999664306641</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>32.54805755615234</v>
+        <v>32.54806900024414</v>
       </c>
       <c r="C31" t="n">
         <v>61.47000122070312</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>33.40056991577148</v>
+        <v>33.40056610107422</v>
       </c>
       <c r="C32" t="n">
         <v>63.08000183105469</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>33.53924179077148</v>
+        <v>33.53925323486328</v>
       </c>
       <c r="C34" t="n">
         <v>62.88999938964844</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>28.14758491516113</v>
+        <v>28.1475944519043</v>
       </c>
       <c r="C35" t="n">
         <v>52.77999877929688</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>30.9904613494873</v>
+        <v>30.9904670715332</v>
       </c>
       <c r="C36" t="n">
         <v>57.59999847412109</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>29.67768478393555</v>
+        <v>29.67768287658691</v>
       </c>
       <c r="C37" t="n">
         <v>55.15999984741211</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.86086273193359</v>
+        <v>22.86085510253906</v>
       </c>
       <c r="C38" t="n">
         <v>42.4900016784668</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>22.39185333251953</v>
+        <v>22.391845703125</v>
       </c>
       <c r="C39" t="n">
         <v>41.18000030517578</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>26.76364326477051</v>
+        <v>26.76363372802734</v>
       </c>
       <c r="C40" t="n">
         <v>49.22000122070312</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>28.46015930175781</v>
+        <v>28.46016311645508</v>
       </c>
       <c r="C41" t="n">
         <v>52.34000015258789</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>28.04848480224609</v>
+        <v>28.04846954345703</v>
       </c>
       <c r="C42" t="n">
         <v>51.13999938964844</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>27.41774940490723</v>
+        <v>27.41775321960449</v>
       </c>
       <c r="C43" t="n">
         <v>49.9900016784668</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>29.46901702880859</v>
+        <v>29.46902275085449</v>
       </c>
       <c r="C44" t="n">
         <v>53.72999954223633</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>29.57305908203125</v>
+        <v>29.57305335998535</v>
       </c>
       <c r="C45" t="n">
         <v>53.45999908447266</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>31.23813629150391</v>
+        <v>31.23812866210938</v>
       </c>
       <c r="C46" t="n">
         <v>56.47000122070312</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>29.69475936889648</v>
+        <v>29.69476509094238</v>
       </c>
       <c r="C47" t="n">
         <v>53.68000030517578</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>32.03959655761719</v>
+        <v>32.03961181640625</v>
       </c>
       <c r="C48" t="n">
         <v>57.47000122070312</v>
@@ -1381,11 +1393,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>31.98384666442871</v>
+        <v>31.98384475708008</v>
       </c>
       <c r="C49" t="n">
         <v>57.36999893188477</v>
@@ -1406,7 +1418,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1431,11 +1443,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>33.01955795288086</v>
+        <v>33.01956558227539</v>
       </c>
       <c r="C51" t="n">
         <v>58.7400016784668</v>
@@ -1456,11 +1468,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>36.20684432983398</v>
+        <v>36.20683670043945</v>
       </c>
       <c r="C52" t="n">
         <v>64.41000366210938</v>
@@ -1481,7 +1493,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1506,11 +1518,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>35.52404403686523</v>
+        <v>35.52402877807617</v>
       </c>
       <c r="C54" t="n">
         <v>62.7599983215332</v>
@@ -1531,7 +1543,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1556,11 +1568,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>36.79194641113281</v>
+        <v>36.79194259643555</v>
       </c>
       <c r="C56" t="n">
         <v>65</v>
@@ -1581,11 +1593,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>36.37487030029297</v>
+        <v>36.3748779296875</v>
       </c>
       <c r="C57" t="n">
         <v>63.79999923706055</v>
@@ -1606,11 +1618,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>38.02257537841797</v>
+        <v>38.0225715637207</v>
       </c>
       <c r="C58" t="n">
         <v>66.69000244140625</v>
@@ -1631,11 +1643,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>38.39316177368164</v>
+        <v>38.39316558837891</v>
       </c>
       <c r="C59" t="n">
         <v>67.33999633789062</v>
@@ -1656,7 +1668,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>41.66454696655273</v>
+        <v>41.66454315185547</v>
       </c>
       <c r="C61" t="n">
         <v>72.58000183105469</v>
@@ -1706,11 +1718,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>41.11344528198242</v>
+        <v>41.11344146728516</v>
       </c>
       <c r="C62" t="n">
         <v>71.62000274658203</v>
@@ -1731,11 +1743,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>42.66233825683594</v>
+        <v>42.66233444213867</v>
       </c>
       <c r="C63" t="n">
         <v>73.80000305175781</v>
@@ -1760,11 +1772,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>42.96294403076172</v>
+        <v>42.96294021606445</v>
       </c>
       <c r="C64" t="n">
         <v>74.31999969482422</v>
@@ -1789,11 +1801,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>43.33867263793945</v>
+        <v>43.33869552612305</v>
       </c>
       <c r="C65" t="n">
         <v>74.97000122070312</v>
@@ -1818,11 +1830,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>42.78113174438477</v>
+        <v>42.7811279296875</v>
       </c>
       <c r="C66" t="n">
         <v>73.48999786376953</v>
@@ -1847,7 +1859,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1876,11 +1888,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>40.29543685913086</v>
+        <v>40.29541778564453</v>
       </c>
       <c r="C68" t="n">
         <v>69.22000122070312</v>
@@ -1905,7 +1917,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1934,11 +1946,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>37.05796051025391</v>
+        <v>37.05794906616211</v>
       </c>
       <c r="C70" t="n">
         <v>63.15000152587891</v>
@@ -1963,11 +1975,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.21854782104492</v>
+        <v>41.21853637695312</v>
       </c>
       <c r="C71" t="n">
         <v>70.23999786376953</v>
@@ -1992,11 +2004,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>42.41289901733398</v>
+        <v>42.41289520263672</v>
       </c>
       <c r="C72" t="n">
         <v>71.75</v>
@@ -2021,11 +2033,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.26411437988281</v>
+        <v>43.26409912109375</v>
       </c>
       <c r="C73" t="n">
         <v>73.19000244140625</v>
@@ -2050,11 +2062,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>44.7182502746582</v>
+        <v>44.71826171875</v>
       </c>
       <c r="C74" t="n">
         <v>75.65000152587891</v>
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>45.85097122192383</v>
+        <v>45.85095977783203</v>
       </c>
       <c r="C75" t="n">
         <v>76.98999786376953</v>
@@ -2108,11 +2120,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>48.07234573364258</v>
+        <v>48.07233810424805</v>
       </c>
       <c r="C76" t="n">
         <v>80.72000122070312</v>
@@ -2137,11 +2149,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>46.53584671020508</v>
+        <v>46.53585433959961</v>
       </c>
       <c r="C77" t="n">
         <v>78.13999938964844</v>
@@ -2166,11 +2178,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>44.96231079101562</v>
+        <v>44.96229553222656</v>
       </c>
       <c r="C78" t="n">
         <v>74.94000244140625</v>
@@ -2195,11 +2207,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>47.25422668457031</v>
+        <v>47.25419616699219</v>
       </c>
       <c r="C79" t="n">
         <v>78.76000213623047</v>
@@ -2224,11 +2236,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>45.36427688598633</v>
+        <v>45.36427307128906</v>
       </c>
       <c r="C80" t="n">
         <v>75.61000061035156</v>
@@ -2253,11 +2265,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>44.61641311645508</v>
+        <v>44.61640548706055</v>
       </c>
       <c r="C81" t="n">
         <v>73.80999755859375</v>
@@ -2282,11 +2294,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>43.26237487792969</v>
+        <v>43.26237869262695</v>
       </c>
       <c r="C82" t="n">
         <v>71.56999969482422</v>
@@ -2311,11 +2323,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>44.27790069580078</v>
+        <v>44.27788925170898</v>
       </c>
       <c r="C83" t="n">
         <v>73.25</v>
@@ -2340,11 +2352,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>44.55453491210938</v>
+        <v>44.55455017089844</v>
       </c>
       <c r="C84" t="n">
         <v>73.11000061035156</v>
@@ -2369,11 +2381,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>44.93236541748047</v>
+        <v>44.932373046875</v>
       </c>
       <c r="C85" t="n">
         <v>73.73000335693359</v>
@@ -2398,11 +2410,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>48.32072830200195</v>
+        <v>48.32073974609375</v>
       </c>
       <c r="C86" t="n">
         <v>79.29000091552734</v>
@@ -2427,11 +2439,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>50.74377059936523</v>
+        <v>50.74374771118164</v>
       </c>
       <c r="C87" t="n">
         <v>82.65000152587891</v>
@@ -2456,11 +2468,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.73910903930664</v>
+        <v>52.73912811279297</v>
       </c>
       <c r="C88" t="n">
         <v>85.90000152587891</v>
@@ -2485,11 +2497,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>52.70228576660156</v>
+        <v>52.70230865478516</v>
       </c>
       <c r="C89" t="n">
         <v>85.83999633789062</v>
@@ -2514,11 +2526,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>53.10895919799805</v>
+        <v>53.10897827148438</v>
       </c>
       <c r="C90" t="n">
         <v>85.90000152587891</v>
@@ -2543,7 +2555,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2572,11 +2584,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>53.66542434692383</v>
+        <v>53.66542816162109</v>
       </c>
       <c r="C92" t="n">
         <v>86.80000305175781</v>
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>53.2889404296875</v>
+        <v>53.28894805908203</v>
       </c>
       <c r="C93" t="n">
         <v>85.58000183105469</v>
@@ -2630,11 +2642,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>56.89424896240234</v>
+        <v>56.89425659179688</v>
       </c>
       <c r="C94" t="n">
         <v>91.37000274658203</v>
@@ -2659,11 +2671,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>61.17205810546875</v>
+        <v>61.17206573486328</v>
       </c>
       <c r="C95" t="n">
         <v>98.23999786376953</v>
@@ -2688,11 +2700,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>64.1435546875</v>
+        <v>64.14354705810547</v>
       </c>
       <c r="C96" t="n">
         <v>102.379997253418</v>
@@ -2717,11 +2729,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>65.83518981933594</v>
+        <v>65.83515930175781</v>
       </c>
       <c r="C97" t="n">
         <v>105.0800018310547</v>
@@ -2746,11 +2758,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>59.66392517089844</v>
+        <v>59.66391754150391</v>
       </c>
       <c r="C98" t="n">
         <v>95.23000335693359</v>
@@ -2775,11 +2787,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>60.42759704589844</v>
+        <v>60.42758941650391</v>
       </c>
       <c r="C99" t="n">
         <v>95.76999664306641</v>
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>61.44347763061523</v>
+        <v>61.44345855712891</v>
       </c>
       <c r="C100" t="n">
         <v>97.37999725341797</v>
@@ -2833,11 +2845,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>62.1501579284668</v>
+        <v>62.150146484375</v>
       </c>
       <c r="C101" t="n">
         <v>98.5</v>
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>65.97793579101562</v>
+        <v>65.97795104980469</v>
       </c>
       <c r="C102" t="n">
         <v>103.879997253418</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>65.20310211181641</v>
+        <v>65.20306396484375</v>
       </c>
       <c r="C103" t="n">
         <v>102.6600036621094</v>
@@ -2920,7 +2932,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2949,11 +2961,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>62.24946594238281</v>
+        <v>62.24948501586914</v>
       </c>
       <c r="C105" t="n">
         <v>97.33000183105469</v>
@@ -2978,7 +2990,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3007,11 +3019,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>67.09740447998047</v>
+        <v>67.097412109375</v>
       </c>
       <c r="C107" t="n">
         <v>104.9100036621094</v>
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3065,11 +3077,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>71.54242706298828</v>
+        <v>71.54244232177734</v>
       </c>
       <c r="C109" t="n">
         <v>111.1699981689453</v>
@@ -3094,11 +3106,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>63.60755920410156</v>
+        <v>63.60757446289062</v>
       </c>
       <c r="C110" t="n">
         <v>98.83999633789062</v>
@@ -3123,11 +3135,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>65.93645477294922</v>
+        <v>65.93644714355469</v>
       </c>
       <c r="C111" t="n">
         <v>101.7300033569336</v>
@@ -3152,7 +3164,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3181,11 +3193,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>65.15866088867188</v>
+        <v>65.15867614746094</v>
       </c>
       <c r="C113" t="n">
         <v>100.5299987792969</v>
@@ -3210,11 +3222,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>64.78523254394531</v>
+        <v>64.78524780273438</v>
       </c>
       <c r="C114" t="n">
         <v>99.22000122070312</v>
@@ -3239,11 +3251,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>63.27695083618164</v>
+        <v>63.27693176269531</v>
       </c>
       <c r="C115" t="n">
         <v>96.91000366210938</v>
@@ -3268,7 +3280,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3297,11 +3309,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>64.21604919433594</v>
+        <v>64.21603393554688</v>
       </c>
       <c r="C117" t="n">
         <v>97.65000152587891</v>
@@ -3326,11 +3338,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>64.89993286132812</v>
+        <v>64.89992523193359</v>
       </c>
       <c r="C118" t="n">
         <v>98.69000244140625</v>
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>67.74742889404297</v>
+        <v>67.74742126464844</v>
       </c>
       <c r="C119" t="n">
         <v>103.0199966430664</v>
@@ -3384,11 +3396,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>68.21600341796875</v>
+        <v>68.21601867675781</v>
       </c>
       <c r="C120" t="n">
         <v>103.0100021362305</v>
@@ -3413,11 +3425,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>63.72611999511719</v>
+        <v>63.72613143920898</v>
       </c>
       <c r="C121" t="n">
         <v>96.23000335693359</v>
@@ -3442,7 +3454,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3471,7 +3483,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3500,11 +3512,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>70.40373992919922</v>
+        <v>70.40374755859375</v>
       </c>
       <c r="C124" t="n">
         <v>105.4700012207031</v>
@@ -3529,7 +3541,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3558,11 +3570,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>69.34297180175781</v>
+        <v>69.34294891357422</v>
       </c>
       <c r="C126" t="n">
         <v>103.0899963378906</v>
@@ -3587,7 +3599,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3616,11 +3628,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>72.71291351318359</v>
+        <v>72.71295166015625</v>
       </c>
       <c r="C128" t="n">
         <v>108.0999984741211</v>
@@ -3645,11 +3657,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>73.98665618896484</v>
+        <v>73.98667144775391</v>
       </c>
       <c r="C129" t="n">
         <v>109.2200012207031</v>
@@ -3674,11 +3686,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>74.08148956298828</v>
+        <v>74.08149719238281</v>
       </c>
       <c r="C130" t="n">
         <v>109.3600006103516</v>
@@ -3703,11 +3715,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>72.99765014648438</v>
+        <v>72.99764251708984</v>
       </c>
       <c r="C131" t="n">
         <v>107.7600021362305</v>
@@ -3732,11 +3744,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>79.07586669921875</v>
+        <v>79.07587432861328</v>
       </c>
       <c r="C132" t="n">
         <v>115.9199981689453</v>
@@ -3761,11 +3773,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>78.20270538330078</v>
+        <v>78.20269012451172</v>
       </c>
       <c r="C133" t="n">
         <v>114.6399993896484</v>
@@ -3790,7 +3802,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3819,11 +3831,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>72.69859313964844</v>
+        <v>72.6986083984375</v>
       </c>
       <c r="C135" t="n">
         <v>105.7600021362305</v>
@@ -3848,11 +3860,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>73.75719451904297</v>
+        <v>73.75718688964844</v>
       </c>
       <c r="C136" t="n">
         <v>107.3000030517578</v>
@@ -3877,7 +3889,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3906,11 +3918,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>73.42278289794922</v>
+        <v>73.42277526855469</v>
       </c>
       <c r="C138" t="n">
         <v>105.9700012207031</v>
@@ -3935,11 +3947,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>76.62383270263672</v>
+        <v>76.62382507324219</v>
       </c>
       <c r="C139" t="n">
         <v>110.5899963378906</v>
@@ -3964,7 +3976,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3993,11 +4005,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>79.82532501220703</v>
+        <v>79.82533264160156</v>
       </c>
       <c r="C141" t="n">
         <v>114.3600006103516</v>
@@ -4022,11 +4034,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>83.82496643066406</v>
+        <v>83.82498168945312</v>
       </c>
       <c r="C142" t="n">
         <v>120.0899963378906</v>
@@ -4051,11 +4063,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>82.03804016113281</v>
+        <v>82.03803253173828</v>
       </c>
       <c r="C143" t="n">
         <v>117.5299987792969</v>
@@ -4080,11 +4092,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>85.40409851074219</v>
+        <v>85.40411376953125</v>
       </c>
       <c r="C144" t="n">
         <v>121.4499969482422</v>
@@ -4109,7 +4121,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4138,11 +4150,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>89.53189086914062</v>
+        <v>89.53189849853516</v>
       </c>
       <c r="C146" t="n">
         <v>127.3199996948242</v>
@@ -4167,7 +4179,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4196,11 +4208,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>74.22090911865234</v>
+        <v>74.22089385986328</v>
       </c>
       <c r="C148" t="n">
         <v>104.6600036621094</v>
@@ -4225,11 +4237,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>80.48990631103516</v>
+        <v>80.48989868164062</v>
       </c>
       <c r="C149" t="n">
         <v>113.5</v>
@@ -4254,11 +4266,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>82.99568939208984</v>
+        <v>82.99568176269531</v>
       </c>
       <c r="C150" t="n">
         <v>116.120002746582</v>
@@ -4283,11 +4295,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>75.92691802978516</v>
+        <v>75.92691040039062</v>
       </c>
       <c r="C151" t="n">
         <v>106.2300033569336</v>
@@ -4312,11 +4324,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>85.69026184082031</v>
+        <v>85.69025421142578</v>
       </c>
       <c r="C152" t="n">
         <v>119.8899993896484</v>
@@ -4341,7 +4353,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4370,11 +4382,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>84.07770538330078</v>
+        <v>84.07769775390625</v>
       </c>
       <c r="C154" t="n">
         <v>116.75</v>
@@ -4399,11 +4411,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>76.72495269775391</v>
+        <v>76.72494506835938</v>
       </c>
       <c r="C155" t="n">
         <v>106.5400009155273</v>
@@ -4428,11 +4440,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>83.71602630615234</v>
+        <v>83.71604156494141</v>
       </c>
       <c r="C156" t="n">
         <v>115.2900009155273</v>
@@ -4457,7 +4469,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4486,11 +4498,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>76.53457641601562</v>
+        <v>76.53456115722656</v>
       </c>
       <c r="C158" t="n">
         <v>105.4000015258789</v>
@@ -4515,11 +4527,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>80.72220611572266</v>
+        <v>80.72219848632812</v>
       </c>
       <c r="C159" t="n">
         <v>110.1999969482422</v>
@@ -4544,7 +4556,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4573,11 +4585,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>77.80680847167969</v>
+        <v>77.80683135986328</v>
       </c>
       <c r="C161" t="n">
         <v>106.2200012207031</v>
@@ -4602,11 +4614,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>68.71562194824219</v>
+        <v>68.71562957763672</v>
       </c>
       <c r="C162" t="n">
         <v>92.91999816894531</v>
@@ -4631,11 +4643,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>76.36957550048828</v>
+        <v>76.36959838867188</v>
       </c>
       <c r="C163" t="n">
         <v>103.2699966430664</v>
@@ -4660,11 +4672,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>88.34970855712891</v>
+        <v>88.34973907470703</v>
       </c>
       <c r="C164" t="n">
         <v>119.4700012207031</v>
@@ -4689,7 +4701,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4718,11 +4730,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>89.36174011230469</v>
+        <v>89.36172485351562</v>
       </c>
       <c r="C166" t="n">
         <v>119.8199996948242</v>
@@ -4747,11 +4759,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>85.89376068115234</v>
+        <v>85.89376831054688</v>
       </c>
       <c r="C167" t="n">
         <v>115.1699981689453</v>
@@ -4776,11 +4788,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>89.99085998535156</v>
+        <v>89.9908447265625</v>
       </c>
       <c r="C168" t="n">
         <v>119.7300033569336</v>
@@ -4805,11 +4817,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>87.98403167724609</v>
+        <v>87.98404693603516</v>
       </c>
       <c r="C169" t="n">
         <v>117.0599975585938</v>
@@ -4834,7 +4846,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4863,11 +4875,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>68.68756103515625</v>
+        <v>68.68757629394531</v>
       </c>
       <c r="C171" t="n">
         <v>90.48999786376953</v>
@@ -4892,7 +4904,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4921,11 +4933,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>71.85285186767578</v>
+        <v>71.85286712646484</v>
       </c>
       <c r="C173" t="n">
         <v>94.66000366210938</v>
@@ -4950,11 +4962,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>76.47990417480469</v>
+        <v>76.47993469238281</v>
       </c>
       <c r="C174" t="n">
         <v>99.70999908447266</v>
@@ -4979,11 +4991,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>85.27767181396484</v>
+        <v>85.27767944335938</v>
       </c>
       <c r="C175" t="n">
         <v>111.1800003051758</v>
@@ -5008,11 +5020,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>109.5002975463867</v>
+        <v>109.5003051757812</v>
       </c>
       <c r="C176" t="n">
         <v>142.7599945068359</v>
@@ -5037,11 +5049,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>126.2998809814453</v>
+        <v>126.299919128418</v>
       </c>
       <c r="C177" t="n">
         <v>163.6199951171875</v>
@@ -5066,7 +5078,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5095,11 +5107,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>121.2748031616211</v>
+        <v>121.2747650146484</v>
       </c>
       <c r="C179" t="n">
         <v>157.1100006103516</v>
@@ -5124,7 +5136,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5153,11 +5165,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>130.7823181152344</v>
+        <v>130.7823028564453</v>
       </c>
       <c r="C181" t="n">
         <v>168.3999938964844</v>
@@ -5182,11 +5194,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>120.3756713867188</v>
+        <v>120.3756103515625</v>
       </c>
       <c r="C182" t="n">
         <v>155</v>
@@ -5211,7 +5223,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5240,11 +5252,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>132.8530120849609</v>
+        <v>132.8529815673828</v>
       </c>
       <c r="C184" t="n">
         <v>169.9900054931641</v>
@@ -5269,11 +5281,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>159.3235778808594</v>
+        <v>159.3235626220703</v>
       </c>
       <c r="C185" t="n">
         <v>203.8600006103516</v>
@@ -5298,11 +5310,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>168.5207061767578</v>
+        <v>168.5207214355469</v>
       </c>
       <c r="C186" t="n">
         <v>214.6000061035156</v>
@@ -5327,11 +5339,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>163.3143005371094</v>
+        <v>163.3142852783203</v>
       </c>
       <c r="C187" t="n">
         <v>207.9700012207031</v>
@@ -5356,7 +5368,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5385,11 +5397,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>154.4357147216797</v>
+        <v>154.4356994628906</v>
       </c>
       <c r="C189" t="n">
         <v>195.6300048828125</v>
@@ -5414,11 +5426,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>143.7547454833984</v>
+        <v>143.7547302246094</v>
       </c>
       <c r="C190" t="n">
         <v>182.1000061035156</v>
@@ -5443,7 +5455,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5472,11 +5484,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>157.3724212646484</v>
+        <v>157.3724517822266</v>
       </c>
       <c r="C192" t="n">
         <v>198.3699951171875</v>
@@ -5501,11 +5513,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>170.0418853759766</v>
+        <v>170.0419006347656</v>
       </c>
       <c r="C193" t="n">
         <v>214.3399963378906</v>
@@ -5530,7 +5542,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5559,11 +5571,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>168.1449737548828</v>
+        <v>168.1450042724609</v>
       </c>
       <c r="C195" t="n">
         <v>210.4199981689453</v>
@@ -5588,11 +5600,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>171.3733367919922</v>
+        <v>171.3733215332031</v>
       </c>
       <c r="C196" t="n">
         <v>214.4600067138672</v>
@@ -5617,7 +5629,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5646,7 +5658,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5675,7 +5687,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5704,11 +5716,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>157.0714874267578</v>
+        <v>157.0715179443359</v>
       </c>
       <c r="C200" t="n">
         <v>194.8899993896484</v>
@@ -5733,11 +5745,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>157.9395294189453</v>
+        <v>157.9395446777344</v>
       </c>
       <c r="C201" t="n">
         <v>194.5099945068359</v>
@@ -5762,11 +5774,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>131.1683197021484</v>
+        <v>131.1683349609375</v>
       </c>
       <c r="C202" t="n">
         <v>161.5399932861328</v>
@@ -5791,7 +5803,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5820,11 +5832,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>155.4993743896484</v>
+        <v>155.4993896484375</v>
       </c>
       <c r="C204" t="n">
         <v>189.7299957275391</v>
@@ -5849,11 +5861,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>142.4761962890625</v>
+        <v>142.4762115478516</v>
       </c>
       <c r="C205" t="n">
         <v>173.8399963378906</v>
@@ -5878,11 +5890,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>151.8112640380859</v>
+        <v>151.811279296875</v>
       </c>
       <c r="C206" t="n">
         <v>185.2299957275391</v>
@@ -5907,7 +5919,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5936,11 +5948,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>160.3911743164062</v>
+        <v>160.3911590576172</v>
       </c>
       <c r="C208" t="n">
         <v>193.9900054931641</v>
@@ -5965,7 +5977,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5994,11 +6006,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>139.4024200439453</v>
+        <v>139.4024353027344</v>
       </c>
       <c r="C210" t="n">
         <v>167</v>
@@ -6023,11 +6035,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>149.6280670166016</v>
+        <v>149.6280517578125</v>
       </c>
       <c r="C211" t="n">
         <v>179.25</v>
@@ -6052,11 +6064,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>156.2058410644531</v>
+        <v>156.2058563232422</v>
       </c>
       <c r="C212" t="n">
         <v>187.1300048828125</v>
@@ -6081,11 +6093,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>142.6872863769531</v>
+        <v>142.6872711181641</v>
       </c>
       <c r="C213" t="n">
         <v>169.3999938964844</v>
@@ -6110,7 +6122,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6139,11 +6151,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>118.9762802124023</v>
+        <v>118.9762878417969</v>
       </c>
       <c r="C215" t="n">
         <v>141.25</v>
@@ -6168,11 +6180,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>129.1981201171875</v>
+        <v>129.1981353759766</v>
       </c>
       <c r="C216" t="n">
         <v>151.6100006103516</v>
@@ -6197,11 +6209,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>133.9873504638672</v>
+        <v>133.9873809814453</v>
       </c>
       <c r="C217" t="n">
         <v>157.2299957275391</v>
@@ -6226,7 +6238,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6255,11 +6267,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>127.7602157592773</v>
+        <v>127.7601776123047</v>
       </c>
       <c r="C219" t="n">
         <v>148.2599945068359</v>
@@ -6284,7 +6296,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6313,11 +6325,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>127.0880584716797</v>
+        <v>127.0880508422852</v>
       </c>
       <c r="C221" t="n">
         <v>147.4799957275391</v>
@@ -6342,11 +6354,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>121.0529556274414</v>
+        <v>121.0529403686523</v>
       </c>
       <c r="C222" t="n">
         <v>138.9299926757812</v>
@@ -6371,7 +6383,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6400,11 +6412,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>113.5944061279297</v>
+        <v>113.5943984985352</v>
       </c>
       <c r="C224" t="n">
         <v>130.3699951171875</v>
@@ -6429,11 +6441,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>113.4347381591797</v>
+        <v>113.4347457885742</v>
       </c>
       <c r="C225" t="n">
         <v>128.5500030517578</v>
@@ -6458,7 +6470,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6487,7 +6499,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6516,11 +6528,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>121.2356338500977</v>
+        <v>121.2356185913086</v>
       </c>
       <c r="C228" t="n">
         <v>135.7200012207031</v>
@@ -6545,11 +6557,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>112.6422882080078</v>
+        <v>112.6422958374023</v>
       </c>
       <c r="C229" t="n">
         <v>126.0999984741211</v>
@@ -6574,11 +6586,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>102.0391006469727</v>
+        <v>102.0390930175781</v>
       </c>
       <c r="C230" t="n">
         <v>114.2300033569336</v>
@@ -6603,11 +6615,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>107.8486938476562</v>
+        <v>107.8486862182617</v>
       </c>
       <c r="C231" t="n">
         <v>119.0299987792969</v>
@@ -6632,7 +6644,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6661,7 +6673,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6690,11 +6702,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>89.83143615722656</v>
+        <v>89.83144378662109</v>
       </c>
       <c r="C234" t="n">
         <v>97.54000091552734</v>
@@ -6719,7 +6731,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6748,7 +6760,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6777,7 +6789,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6806,11 +6818,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>78.38146209716797</v>
+        <v>78.3814697265625</v>
       </c>
       <c r="C238" t="n">
         <v>83.52999877929688</v>
@@ -6835,11 +6847,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>90.47697448730469</v>
+        <v>90.47696685791016</v>
       </c>
       <c r="C239" t="n">
         <v>96.41999816894531</v>
@@ -6864,7 +6876,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6893,11 +6905,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>94.69426727294922</v>
+        <v>94.69427490234375</v>
       </c>
       <c r="C241" t="n">
         <v>99.19000244140625</v>
@@ -6922,11 +6934,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>101.4056396484375</v>
+        <v>101.405632019043</v>
       </c>
       <c r="C242" t="n">
         <v>106.2200012207031</v>
@@ -6951,7 +6963,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6980,7 +6992,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7009,7 +7021,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7038,7 +7050,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7067,7 +7079,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7096,7 +7108,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7154,32 +7166,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>95.81999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C250" t="n">
-        <v>95.81999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="D250" t="n">
-        <v>72074600</v>
+        <v>80563600</v>
       </c>
       <c r="E250" t="n">
         <v>5.379999999999999</v>
       </c>
       <c r="F250" t="n">
-        <v>17.81040886520897</v>
+        <v>17.10966599475053</v>
       </c>
       <c r="G250" t="n">
         <v>851000000</v>
       </c>
       <c r="H250" t="n">
-        <v>81542819740.29541</v>
+        <v>78334552597.0459</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08469400705052879</v>
+        <v>0.09466933019976498</v>
       </c>
     </row>
   </sheetData>
@@ -7211,75 +7223,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7483,13 +7495,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7516,7 +7528,7 @@
       <c r="I7" t="n">
         <v>2.14</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K7" t="n">
@@ -7529,13 +7541,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7562,7 +7574,7 @@
       <c r="I8" t="n">
         <v>2.27</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K8" t="n">
@@ -7575,13 +7587,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7608,7 +7620,7 @@
       <c r="I9" t="n">
         <v>2.67</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K9" t="n">
@@ -7621,13 +7633,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7654,7 +7666,7 @@
       <c r="I10" t="n">
         <v>3.11</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7667,13 +7679,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7700,7 +7712,7 @@
       <c r="I11" t="n">
         <v>3.47</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K11" t="n">
@@ -7713,13 +7725,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7746,7 +7758,7 @@
       <c r="I12" t="n">
         <v>3.82</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K12" t="n">
@@ -7759,13 +7771,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7792,7 +7804,7 @@
       <c r="I13" t="n">
         <v>4.050000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7805,13 +7817,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7838,7 +7850,7 @@
       <c r="I14" t="n">
         <v>4.12</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K14" t="n">
@@ -7851,13 +7863,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7884,7 +7896,7 @@
       <c r="I15" t="n">
         <v>3.75</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K15" t="n">
@@ -7897,13 +7909,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7930,7 +7942,7 @@
       <c r="I16" t="n">
         <v>3.87</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K16" t="n">
@@ -7943,13 +7955,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7976,7 +7988,7 @@
       <c r="I17" t="n">
         <v>3.95</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K17" t="n">
@@ -7989,13 +8001,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8022,7 +8034,7 @@
       <c r="I18" t="n">
         <v>3.37</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K18" t="n">
@@ -8035,13 +8047,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8068,7 +8080,7 @@
       <c r="I19" t="n">
         <v>0.7999999999999996</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8081,13 +8093,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8114,7 +8126,7 @@
       <c r="I20" t="n">
         <v>0.8799999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K20" t="n">
@@ -8127,13 +8139,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8160,7 +8172,7 @@
       <c r="I21" t="n">
         <v>0.8599999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K21" t="n">
@@ -8173,13 +8185,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8206,7 +8218,7 @@
       <c r="I22" t="n">
         <v>1.54</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K22" t="n">
@@ -8219,13 +8231,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8252,7 +8264,7 @@
       <c r="I23" t="n">
         <v>4.62</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K23" t="n">
@@ -8265,13 +8277,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8298,7 +8310,7 @@
       <c r="I24" t="n">
         <v>4.52</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K24" t="n">
@@ -8311,13 +8323,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8344,7 +8356,7 @@
       <c r="I25" t="n">
         <v>3.88</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K25" t="n">
@@ -8357,13 +8369,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8390,7 +8402,7 @@
       <c r="I26" t="n">
         <v>4.04</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K26" t="n">
@@ -8403,13 +8415,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8436,7 +8448,7 @@
       <c r="I27" t="n">
         <v>3.28</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K27" t="n">
@@ -8449,13 +8461,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8482,7 +8494,7 @@
       <c r="I28" t="n">
         <v>3.42</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K28" t="n">
@@ -8495,13 +8507,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8528,7 +8540,7 @@
       <c r="I29" t="n">
         <v>4.28</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K29" t="n">
@@ -8541,13 +8553,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8574,7 +8586,7 @@
       <c r="I30" t="n">
         <v>4.35</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K30" t="n">
@@ -8587,13 +8599,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8620,7 +8632,7 @@
       <c r="I31" t="n">
         <v>5.34</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K31" t="n">
@@ -8633,13 +8645,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8666,7 +8678,7 @@
       <c r="I32" t="n">
         <v>5.49</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="K32" t="n">
@@ -8679,13 +8691,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8712,7 +8724,7 @@
       <c r="I33" t="n">
         <v>5.57</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K33" t="n">
@@ -8725,13 +8737,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8758,7 +8770,7 @@
       <c r="I34" t="n">
         <v>5.619999999999999</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K34" t="n">
@@ -8771,13 +8783,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8804,7 +8816,7 @@
       <c r="I35" t="n">
         <v>3.87</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="K35" t="n">
@@ -8817,13 +8829,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8850,7 +8862,7 @@
       <c r="I36" t="n">
         <v>3.92</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K36" t="n">
@@ -8863,13 +8875,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8896,7 +8908,7 @@
       <c r="I37" t="n">
         <v>4.07</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K37" t="n">
@@ -8909,13 +8921,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8942,7 +8954,7 @@
       <c r="I38" t="n">
         <v>4.08</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K38" t="n">
@@ -8955,13 +8967,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8988,7 +9000,7 @@
       <c r="I39" t="n">
         <v>5.62</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="K39" t="n">
@@ -9001,13 +9013,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9034,7 +9046,7 @@
       <c r="I40" t="n">
         <v>5.85</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K40" t="n">
@@ -9047,13 +9059,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9080,7 +9092,7 @@
       <c r="I41" t="n">
         <v>5.98</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K41" t="n">
@@ -9093,13 +9105,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9126,7 +9138,7 @@
       <c r="I42" t="n">
         <v>6.26</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K42" t="n">
@@ -9139,13 +9151,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9172,7 +9184,7 @@
       <c r="I43" t="n">
         <v>5.51</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K43" t="n">
@@ -9185,13 +9197,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9218,7 +9230,7 @@
       <c r="I44" t="n">
         <v>5.24</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K44" t="n">
@@ -9231,13 +9243,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9264,7 +9276,7 @@
       <c r="I45" t="n">
         <v>5.47</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="K45" t="n">
@@ -9277,13 +9289,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9310,7 +9322,7 @@
       <c r="I46" t="n">
         <v>5.75</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="K46" t="n">
@@ -9323,13 +9335,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9356,7 +9368,7 @@
       <c r="I47" t="n">
         <v>5.11</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K47" t="n">
@@ -9369,13 +9381,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9402,7 +9414,7 @@
       <c r="I48" t="n">
         <v>4.94</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="K48" t="n">
@@ -9415,13 +9427,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9448,7 +9460,7 @@
       <c r="I49" t="n">
         <v>5.029999999999999</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K49" t="n">
@@ -9461,13 +9473,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9494,7 +9506,7 @@
       <c r="I50" t="n">
         <v>5.26</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="K50" t="n">
@@ -9507,13 +9519,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44249</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9540,7 +9552,7 @@
       <c r="I51" t="n">
         <v>1.54</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44249</v>
       </c>
       <c r="K51" t="n">
@@ -9553,13 +9565,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9586,7 +9598,7 @@
       <c r="I52" t="n">
         <v>5.899999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K52" t="n">
@@ -9599,13 +9611,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9632,7 +9644,7 @@
       <c r="I53" t="n">
         <v>6.92</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K53" t="n">
@@ -9645,13 +9657,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9678,7 +9690,7 @@
       <c r="I54" t="n">
         <v>7.329999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K54" t="n">
@@ -9691,13 +9703,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9724,7 +9736,7 @@
       <c r="I55" t="n">
         <v>14.68</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K55" t="n">
@@ -9737,13 +9749,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9770,7 +9782,7 @@
       <c r="I56" t="n">
         <v>12.24</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K56" t="n">
@@ -9783,13 +9795,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9816,7 +9828,7 @@
       <c r="I57" t="n">
         <v>12.44</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K57" t="n">
@@ -9829,13 +9841,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9862,7 +9874,7 @@
       <c r="I58" t="n">
         <v>12.75</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K58" t="n">
@@ -9875,13 +9887,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9908,7 +9920,7 @@
       <c r="I59" t="n">
         <v>13.2</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K59" t="n">
@@ -9921,13 +9933,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9954,7 +9966,7 @@
       <c r="I60" t="n">
         <v>12.36</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K60" t="n">
@@ -9967,13 +9979,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10000,7 +10012,7 @@
       <c r="I61" t="n">
         <v>11.53</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="K61" t="n">
@@ -10013,13 +10025,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10046,7 +10058,7 @@
       <c r="I62" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K62" t="n">
@@ -10059,13 +10071,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10092,7 +10104,7 @@
       <c r="I63" t="n">
         <v>7.799999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K63" t="n">
@@ -10105,13 +10117,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10138,7 +10150,7 @@
       <c r="I64" t="n">
         <v>6.91</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K64" t="n">
@@ -10151,13 +10163,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10184,7 +10196,7 @@
       <c r="I65" t="n">
         <v>6.14</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K65" t="n">
@@ -10197,13 +10209,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10230,7 +10242,7 @@
       <c r="I66" t="n">
         <v>6.629999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="K66" t="n">
@@ -10243,13 +10255,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10276,7 +10288,7 @@
       <c r="I67" t="n">
         <v>6.75</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="K67" t="n">
@@ -10289,13 +10301,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10322,7 +10334,7 @@
       <c r="I68" t="n">
         <v>6.85</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K68" t="n">
@@ -10335,13 +10347,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10368,7 +10380,7 @@
       <c r="I69" t="n">
         <v>6.709999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K69" t="n">
@@ -10381,13 +10393,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10414,7 +10426,7 @@
       <c r="I70" t="n">
         <v>6.459999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K70" t="n">
@@ -10427,13 +10439,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10460,7 +10472,7 @@
       <c r="I71" t="n">
         <v>6.559999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="K71" t="n">
@@ -10473,13 +10485,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10506,7 +10518,7 @@
       <c r="I72" t="n">
         <v>6.179999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K72" t="n">
@@ -10519,13 +10531,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10552,7 +10564,7 @@
       <c r="I73" t="n">
         <v>5.379999999999999</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K73" t="n">
@@ -10590,57 +10602,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40115</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C2" t="n">
@@ -10670,10 +10682,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40226</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C3" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C4" t="n">
@@ -10740,10 +10752,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C5" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C6" t="n">
@@ -10814,10 +10826,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10851,10 +10863,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10888,10 +10900,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C9" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C10" t="n">
@@ -10962,10 +10974,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C11" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C12" t="n">
@@ -11036,10 +11048,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C13" t="n">
@@ -11073,10 +11085,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C14" t="n">
@@ -11110,10 +11122,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C15" t="n">
@@ -11147,10 +11159,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C16" t="n">
@@ -11184,10 +11196,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C17" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C18" t="n">
@@ -11258,10 +11270,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C19" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C20" t="n">
@@ -11332,10 +11344,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C21" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C22" t="n">
@@ -11406,10 +11418,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C23" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C24" t="n">
@@ -11480,10 +11492,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C25" t="n">
@@ -11517,10 +11529,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C26" t="n">
@@ -11554,10 +11566,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C27" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C28" t="n">
@@ -11628,10 +11640,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C29" t="n">
@@ -11665,10 +11677,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C30" t="n">
@@ -11702,10 +11714,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C31" t="n">
@@ -11739,10 +11751,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="C32" t="n">
@@ -11776,10 +11788,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C33" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C34" t="n">
@@ -11850,10 +11862,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="C35" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C36" t="n">
@@ -11924,10 +11936,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C37" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C38" t="n">
@@ -11998,10 +12010,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="C39" t="n">
@@ -12035,10 +12047,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C40" t="n">
@@ -12072,10 +12084,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C41" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C42" t="n">
@@ -12146,10 +12158,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C43" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C44" t="n">
@@ -12220,10 +12232,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="C45" t="n">
@@ -12257,10 +12269,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="C46" t="n">
@@ -12294,10 +12306,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C47" t="n">
@@ -12331,10 +12343,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="C48" t="n">
@@ -12368,10 +12380,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C49" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="C50" t="n">
@@ -12442,10 +12454,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44249</v>
       </c>
       <c r="C51" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C52" t="n">
@@ -12516,10 +12528,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C53" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C54" t="n">
@@ -12590,10 +12602,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C55" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C56" t="n">
@@ -12664,10 +12676,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C57" t="n">
@@ -12701,10 +12713,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C58" t="n">
@@ -12738,10 +12750,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C59" t="n">
@@ -12775,10 +12787,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C60" t="n">
@@ -12812,10 +12824,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="C61" t="n">
@@ -12849,10 +12861,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C62" t="n">
@@ -12886,10 +12898,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C63" t="n">
@@ -12923,10 +12935,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C64" t="n">
@@ -12960,10 +12972,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C65" t="n">
@@ -12997,10 +13009,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C66" t="n">
@@ -13034,10 +13046,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C67" t="n">
@@ -13071,10 +13083,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C68" t="n">
@@ -13108,10 +13120,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C69" t="n">
@@ -13145,10 +13157,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C70" t="n">
@@ -13182,10 +13194,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="C71" t="n">
@@ -13219,10 +13231,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C72" t="n">
@@ -13256,10 +13268,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C73" t="n">
@@ -13311,12 +13323,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/UPS.xlsx
+++ b/salidas/empresas/UPS.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>37.53774261474609</v>
+        <v>37.53773498535156</v>
       </c>
       <c r="C2" t="n">
         <v>74.91000366210938</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>37.62490081787109</v>
+        <v>37.62489700317383</v>
       </c>
       <c r="C3" t="n">
         <v>74.70999908447266</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>39.97674942016602</v>
+        <v>39.97677993774414</v>
       </c>
       <c r="C4" t="n">
         <v>79.37999725341797</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>40.8278923034668</v>
+        <v>40.82788467407227</v>
       </c>
       <c r="C5" t="n">
         <v>81.06999969482422</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>40.75290679931641</v>
+        <v>40.7529296875</v>
       </c>
       <c r="C6" t="n">
         <v>80.55000305175781</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>41.65347671508789</v>
+        <v>41.65348434448242</v>
       </c>
       <c r="C7" t="n">
         <v>82.33000183105469</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.86386108398438</v>
+        <v>34.86386489868164</v>
       </c>
       <c r="C8" t="n">
         <v>68.91000366210938</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>36.58959579467773</v>
+        <v>36.58959197998047</v>
       </c>
       <c r="C10" t="n">
         <v>71.94000244140625</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>38.32397842407227</v>
+        <v>38.32395935058594</v>
       </c>
       <c r="C11" t="n">
         <v>75.34999847412109</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>39.82140350341797</v>
+        <v>39.82138824462891</v>
       </c>
       <c r="C12" t="n">
         <v>77.91999816894531</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>36.93904876708984</v>
+        <v>36.93904495239258</v>
       </c>
       <c r="C14" t="n">
         <v>72.27999877929688</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>36.0728874206543</v>
+        <v>36.07289886474609</v>
       </c>
       <c r="C15" t="n">
         <v>70.19000244140625</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>36.02664184570312</v>
+        <v>36.02663803100586</v>
       </c>
       <c r="C16" t="n">
         <v>70.09999847412109</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>36.19623947143555</v>
+        <v>36.19624328613281</v>
       </c>
       <c r="C17" t="n">
         <v>70.43000030517578</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>37.20673370361328</v>
+        <v>37.20674514770508</v>
       </c>
       <c r="C18" t="n">
         <v>71.97000122070312</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>37.73923492431641</v>
+        <v>37.73922348022461</v>
       </c>
       <c r="C19" t="n">
         <v>73</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>39.1453971862793</v>
+        <v>39.14538192749023</v>
       </c>
       <c r="C20" t="n">
         <v>75.72000122070312</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>39.2177848815918</v>
+        <v>39.21776580810547</v>
       </c>
       <c r="C21" t="n">
         <v>75.86000061035156</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>39.0424690246582</v>
+        <v>39.04248046875</v>
       </c>
       <c r="C22" t="n">
         <v>75.09999847412109</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>39.0424690246582</v>
+        <v>39.04248046875</v>
       </c>
       <c r="C23" t="n">
         <v>75.09999847412109</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>38.52489852905273</v>
+        <v>38.5249137878418</v>
       </c>
       <c r="C24" t="n">
         <v>73.68000030517578</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>36.97722625732422</v>
+        <v>36.97722244262695</v>
       </c>
       <c r="C25" t="n">
         <v>70.72000122070312</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>38.15367126464844</v>
+        <v>38.15368270874023</v>
       </c>
       <c r="C26" t="n">
         <v>72.97000122070312</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>36.95800399780273</v>
+        <v>36.95798873901367</v>
       </c>
       <c r="C27" t="n">
         <v>70.23999786376953</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>38.42073440551758</v>
+        <v>38.42073059082031</v>
       </c>
       <c r="C28" t="n">
         <v>73.01999664306641</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>38.09978866577148</v>
+        <v>38.09978103637695</v>
       </c>
       <c r="C29" t="n">
         <v>72.41000366210938</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>37.60475921630859</v>
+        <v>37.60474395751953</v>
       </c>
       <c r="C30" t="n">
         <v>71.01999664306641</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>33.40056610107422</v>
+        <v>33.40055084228516</v>
       </c>
       <c r="C32" t="n">
         <v>63.08000183105469</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>34.19521331787109</v>
+        <v>34.19520950317383</v>
       </c>
       <c r="C33" t="n">
         <v>64.12000274658203</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>33.53925323486328</v>
+        <v>33.53924560546875</v>
       </c>
       <c r="C34" t="n">
         <v>62.88999938964844</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>30.9904670715332</v>
+        <v>30.99047088623047</v>
       </c>
       <c r="C36" t="n">
         <v>57.59999847412109</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>29.67768287658691</v>
+        <v>29.67767906188965</v>
       </c>
       <c r="C37" t="n">
         <v>55.15999984741211</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.86085510253906</v>
+        <v>22.8608512878418</v>
       </c>
       <c r="C38" t="n">
         <v>42.4900016784668</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>22.391845703125</v>
+        <v>22.3918514251709</v>
       </c>
       <c r="C39" t="n">
         <v>41.18000030517578</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>26.76363372802734</v>
+        <v>26.76364707946777</v>
       </c>
       <c r="C40" t="n">
         <v>49.22000122070312</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>28.46016311645508</v>
+        <v>28.46016883850098</v>
       </c>
       <c r="C41" t="n">
         <v>52.34000015258789</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>28.04846954345703</v>
+        <v>28.04848670959473</v>
       </c>
       <c r="C42" t="n">
         <v>51.13999938964844</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>27.41775321960449</v>
+        <v>27.41775131225586</v>
       </c>
       <c r="C43" t="n">
         <v>49.9900016784668</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>29.46902275085449</v>
+        <v>29.46901512145996</v>
       </c>
       <c r="C44" t="n">
         <v>53.72999954223633</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>29.57305335998535</v>
+        <v>29.57305145263672</v>
       </c>
       <c r="C45" t="n">
         <v>53.45999908447266</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>31.23812866210938</v>
+        <v>31.23813629150391</v>
       </c>
       <c r="C46" t="n">
         <v>56.47000122070312</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>29.69476509094238</v>
+        <v>29.69476127624512</v>
       </c>
       <c r="C47" t="n">
         <v>53.68000030517578</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>32.03961181640625</v>
+        <v>32.03960418701172</v>
       </c>
       <c r="C48" t="n">
         <v>57.47000122070312</v>
@@ -1397,7 +1397,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>31.98384475708008</v>
+        <v>31.98385429382324</v>
       </c>
       <c r="C49" t="n">
         <v>57.36999893188477</v>
@@ -1422,7 +1422,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>32.20685195922852</v>
+        <v>32.20684432983398</v>
       </c>
       <c r="C50" t="n">
         <v>57.77000045776367</v>
@@ -1447,7 +1447,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>33.01956558227539</v>
+        <v>33.01956939697266</v>
       </c>
       <c r="C51" t="n">
         <v>58.7400016784668</v>
@@ -1472,7 +1472,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>36.20683670043945</v>
+        <v>36.20684432983398</v>
       </c>
       <c r="C52" t="n">
         <v>64.41000366210938</v>
@@ -1522,7 +1522,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>35.52402877807617</v>
+        <v>35.52403259277344</v>
       </c>
       <c r="C54" t="n">
         <v>62.7599983215332</v>
@@ -1572,7 +1572,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>36.79194259643555</v>
+        <v>36.79193496704102</v>
       </c>
       <c r="C56" t="n">
         <v>65</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>36.3748779296875</v>
+        <v>36.37487030029297</v>
       </c>
       <c r="C57" t="n">
         <v>63.79999923706055</v>
@@ -1622,7 +1622,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>38.0225715637207</v>
+        <v>38.02257537841797</v>
       </c>
       <c r="C58" t="n">
         <v>66.69000244140625</v>
@@ -1647,7 +1647,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>38.39316558837891</v>
+        <v>38.39316940307617</v>
       </c>
       <c r="C59" t="n">
         <v>67.33999633789062</v>
@@ -1672,7 +1672,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>40.25811767578125</v>
+        <v>40.25811004638672</v>
       </c>
       <c r="C60" t="n">
         <v>70.12999725341797</v>
@@ -1697,7 +1697,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>41.66454315185547</v>
+        <v>41.66452789306641</v>
       </c>
       <c r="C61" t="n">
         <v>72.58000183105469</v>
@@ -1722,7 +1722,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>41.11344146728516</v>
+        <v>41.11344528198242</v>
       </c>
       <c r="C62" t="n">
         <v>71.62000274658203</v>
@@ -1747,7 +1747,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>42.66233444213867</v>
+        <v>42.6623420715332</v>
       </c>
       <c r="C63" t="n">
         <v>73.80000305175781</v>
@@ -1776,7 +1776,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>42.96294021606445</v>
+        <v>42.96295166015625</v>
       </c>
       <c r="C64" t="n">
         <v>74.31999969482422</v>
@@ -1805,7 +1805,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>43.33869552612305</v>
+        <v>43.33868789672852</v>
       </c>
       <c r="C65" t="n">
         <v>74.97000122070312</v>
@@ -1834,7 +1834,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>42.7811279296875</v>
+        <v>42.78113174438477</v>
       </c>
       <c r="C66" t="n">
         <v>73.48999786376953</v>
@@ -1892,7 +1892,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>40.29541778564453</v>
+        <v>40.29541397094727</v>
       </c>
       <c r="C68" t="n">
         <v>69.22000122070312</v>
@@ -1921,7 +1921,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>39.54609298706055</v>
+        <v>39.54608154296875</v>
       </c>
       <c r="C69" t="n">
         <v>67.38999938964844</v>
@@ -1950,7 +1950,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>37.05794906616211</v>
+        <v>37.05794525146484</v>
       </c>
       <c r="C70" t="n">
         <v>63.15000152587891</v>
@@ -1979,7 +1979,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.21853637695312</v>
+        <v>41.21854400634766</v>
       </c>
       <c r="C71" t="n">
         <v>70.23999786376953</v>
@@ -2008,7 +2008,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>42.41289520263672</v>
+        <v>42.41288375854492</v>
       </c>
       <c r="C72" t="n">
         <v>71.75</v>
@@ -2037,7 +2037,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.26409912109375</v>
+        <v>43.26409530639648</v>
       </c>
       <c r="C73" t="n">
         <v>73.19000244140625</v>
@@ -2066,7 +2066,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>44.71826171875</v>
+        <v>44.71825408935547</v>
       </c>
       <c r="C74" t="n">
         <v>75.65000152587891</v>
@@ -2095,7 +2095,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>45.85095977783203</v>
+        <v>45.85098266601562</v>
       </c>
       <c r="C75" t="n">
         <v>76.98999786376953</v>
@@ -2124,7 +2124,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>48.07233810424805</v>
+        <v>48.07234954833984</v>
       </c>
       <c r="C76" t="n">
         <v>80.72000122070312</v>
@@ -2153,7 +2153,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>46.53585433959961</v>
+        <v>46.53585052490234</v>
       </c>
       <c r="C77" t="n">
         <v>78.13999938964844</v>
@@ -2182,7 +2182,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>44.96229553222656</v>
+        <v>44.9622917175293</v>
       </c>
       <c r="C78" t="n">
         <v>74.94000244140625</v>
@@ -2211,7 +2211,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>47.25419616699219</v>
+        <v>47.25418853759766</v>
       </c>
       <c r="C79" t="n">
         <v>78.76000213623047</v>
@@ -2240,7 +2240,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>45.36427307128906</v>
+        <v>45.3642692565918</v>
       </c>
       <c r="C80" t="n">
         <v>75.61000061035156</v>
@@ -2269,7 +2269,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>44.61640548706055</v>
+        <v>44.61640167236328</v>
       </c>
       <c r="C81" t="n">
         <v>73.80999755859375</v>
@@ -2327,7 +2327,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>44.27788925170898</v>
+        <v>44.27790069580078</v>
       </c>
       <c r="C83" t="n">
         <v>73.25</v>
@@ -2356,7 +2356,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>44.55455017089844</v>
+        <v>44.55453109741211</v>
       </c>
       <c r="C84" t="n">
         <v>73.11000061035156</v>
@@ -2385,7 +2385,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>44.932373046875</v>
+        <v>44.93236541748047</v>
       </c>
       <c r="C85" t="n">
         <v>73.73000335693359</v>
@@ -2414,7 +2414,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>48.32073974609375</v>
+        <v>48.32071685791016</v>
       </c>
       <c r="C86" t="n">
         <v>79.29000091552734</v>
@@ -2443,7 +2443,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>50.74374771118164</v>
+        <v>50.74375534057617</v>
       </c>
       <c r="C87" t="n">
         <v>82.65000152587891</v>
@@ -2472,7 +2472,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.73912811279297</v>
+        <v>52.73913955688477</v>
       </c>
       <c r="C88" t="n">
         <v>85.90000152587891</v>
@@ -2501,7 +2501,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>52.70230865478516</v>
+        <v>52.7022819519043</v>
       </c>
       <c r="C89" t="n">
         <v>85.83999633789062</v>
@@ -2530,7 +2530,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>53.10897827148438</v>
+        <v>53.1089973449707</v>
       </c>
       <c r="C90" t="n">
         <v>85.90000152587891</v>
@@ -2559,7 +2559,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>53.46756362915039</v>
+        <v>53.46757507324219</v>
       </c>
       <c r="C91" t="n">
         <v>86.48000335693359</v>
@@ -2588,7 +2588,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>53.66542816162109</v>
+        <v>53.66541290283203</v>
       </c>
       <c r="C92" t="n">
         <v>86.80000305175781</v>
@@ -2617,7 +2617,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>53.28894805908203</v>
+        <v>53.2889518737793</v>
       </c>
       <c r="C93" t="n">
         <v>85.58000183105469</v>
@@ -2646,7 +2646,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>56.89425659179688</v>
+        <v>56.89424896240234</v>
       </c>
       <c r="C94" t="n">
         <v>91.37000274658203</v>
@@ -2675,7 +2675,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>61.17206573486328</v>
+        <v>61.17207717895508</v>
       </c>
       <c r="C95" t="n">
         <v>98.23999786376953</v>
@@ -2704,7 +2704,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>64.14354705810547</v>
+        <v>64.1435546875</v>
       </c>
       <c r="C96" t="n">
         <v>102.379997253418</v>
@@ -2733,7 +2733,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>65.83515930175781</v>
+        <v>65.83518981933594</v>
       </c>
       <c r="C97" t="n">
         <v>105.0800018310547</v>
@@ -2762,7 +2762,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>59.66391754150391</v>
+        <v>59.66392135620117</v>
       </c>
       <c r="C98" t="n">
         <v>95.23000335693359</v>
@@ -2791,7 +2791,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>60.42758941650391</v>
+        <v>60.42760467529297</v>
       </c>
       <c r="C99" t="n">
         <v>95.76999664306641</v>
@@ -2820,7 +2820,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>61.44345855712891</v>
+        <v>61.4434814453125</v>
       </c>
       <c r="C100" t="n">
         <v>97.37999725341797</v>
@@ -2849,7 +2849,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>62.150146484375</v>
+        <v>62.1501350402832</v>
       </c>
       <c r="C101" t="n">
         <v>98.5</v>
@@ -2878,7 +2878,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>65.97795104980469</v>
+        <v>65.97795867919922</v>
       </c>
       <c r="C102" t="n">
         <v>103.879997253418</v>
@@ -2907,7 +2907,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>65.20306396484375</v>
+        <v>65.20307159423828</v>
       </c>
       <c r="C103" t="n">
         <v>102.6600036621094</v>
@@ -2936,7 +2936,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>61.66537475585938</v>
+        <v>61.66536712646484</v>
       </c>
       <c r="C104" t="n">
         <v>97.08999633789062</v>
@@ -2965,7 +2965,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>62.24948501586914</v>
+        <v>62.24945068359375</v>
       </c>
       <c r="C105" t="n">
         <v>97.33000183105469</v>
@@ -2994,7 +2994,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>62.86346054077148</v>
+        <v>62.86346435546875</v>
       </c>
       <c r="C106" t="n">
         <v>98.29000091552734</v>
@@ -3023,7 +3023,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>67.097412109375</v>
+        <v>67.09741973876953</v>
       </c>
       <c r="C107" t="n">
         <v>104.9100036621094</v>
@@ -3052,7 +3052,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>70.73801422119141</v>
+        <v>70.73799896240234</v>
       </c>
       <c r="C108" t="n">
         <v>109.9199981689453</v>
@@ -3081,7 +3081,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>71.54244232177734</v>
+        <v>71.54242706298828</v>
       </c>
       <c r="C109" t="n">
         <v>111.1699981689453</v>
@@ -3110,7 +3110,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>63.60757446289062</v>
+        <v>63.60755920410156</v>
       </c>
       <c r="C110" t="n">
         <v>98.83999633789062</v>
@@ -3139,7 +3139,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>65.93644714355469</v>
+        <v>65.93643951416016</v>
       </c>
       <c r="C111" t="n">
         <v>101.7300033569336</v>
@@ -3168,7 +3168,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>62.83180236816406</v>
+        <v>62.83181381225586</v>
       </c>
       <c r="C112" t="n">
         <v>96.94000244140625</v>
@@ -3226,7 +3226,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>64.78524780273438</v>
+        <v>64.78524017333984</v>
       </c>
       <c r="C114" t="n">
         <v>99.22000122070312</v>
@@ -3255,7 +3255,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>63.27693176269531</v>
+        <v>63.27695083618164</v>
       </c>
       <c r="C115" t="n">
         <v>96.91000366210938</v>
@@ -3284,7 +3284,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>66.83549499511719</v>
+        <v>66.83547210693359</v>
       </c>
       <c r="C116" t="n">
         <v>102.3600006103516</v>
@@ -3313,7 +3313,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>64.21603393554688</v>
+        <v>64.21605682373047</v>
       </c>
       <c r="C117" t="n">
         <v>97.65000152587891</v>
@@ -3342,7 +3342,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>64.89992523193359</v>
+        <v>64.89995574951172</v>
       </c>
       <c r="C118" t="n">
         <v>98.69000244140625</v>
@@ -3371,7 +3371,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>67.74742126464844</v>
+        <v>67.74742889404297</v>
       </c>
       <c r="C119" t="n">
         <v>103.0199966430664</v>
@@ -3400,7 +3400,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>68.21601867675781</v>
+        <v>68.21603393554688</v>
       </c>
       <c r="C120" t="n">
         <v>103.0100021362305</v>
@@ -3429,7 +3429,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>63.72613143920898</v>
+        <v>63.72612762451172</v>
       </c>
       <c r="C121" t="n">
         <v>96.23000335693359</v>
@@ -3458,7 +3458,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>61.71956634521484</v>
+        <v>61.71956253051758</v>
       </c>
       <c r="C122" t="n">
         <v>93.19999694824219</v>
@@ -3487,7 +3487,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>64.44942474365234</v>
+        <v>64.44944763183594</v>
       </c>
       <c r="C123" t="n">
         <v>96.55000305175781</v>
@@ -3516,7 +3516,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>70.40374755859375</v>
+        <v>70.40373992919922</v>
       </c>
       <c r="C124" t="n">
         <v>105.4700012207031</v>
@@ -3545,7 +3545,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>70.13674163818359</v>
+        <v>70.13671875</v>
       </c>
       <c r="C125" t="n">
         <v>105.0699996948242</v>
@@ -3574,7 +3574,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>69.34294891357422</v>
+        <v>69.34297180175781</v>
       </c>
       <c r="C126" t="n">
         <v>103.0899963378906</v>
@@ -3632,7 +3632,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>72.71295166015625</v>
+        <v>72.71291351318359</v>
       </c>
       <c r="C128" t="n">
         <v>108.0999984741211</v>
@@ -3661,7 +3661,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>73.98667144775391</v>
+        <v>73.98665618896484</v>
       </c>
       <c r="C129" t="n">
         <v>109.2200012207031</v>
@@ -3690,7 +3690,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>74.08149719238281</v>
+        <v>74.08151245117188</v>
       </c>
       <c r="C130" t="n">
         <v>109.3600006103516</v>
@@ -3719,7 +3719,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>72.99764251708984</v>
+        <v>72.99763488769531</v>
       </c>
       <c r="C131" t="n">
         <v>107.7600021362305</v>
@@ -3748,7 +3748,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>79.07587432861328</v>
+        <v>79.07586669921875</v>
       </c>
       <c r="C132" t="n">
         <v>115.9199981689453</v>
@@ -3864,7 +3864,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>73.75718688964844</v>
+        <v>73.75720977783203</v>
       </c>
       <c r="C136" t="n">
         <v>107.3000030517578</v>
@@ -3893,7 +3893,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>73.86717987060547</v>
+        <v>73.86715698242188</v>
       </c>
       <c r="C137" t="n">
         <v>107.4599990844727</v>
@@ -3922,7 +3922,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>73.42277526855469</v>
+        <v>73.42279815673828</v>
       </c>
       <c r="C138" t="n">
         <v>105.9700012207031</v>
@@ -3951,7 +3951,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>76.62382507324219</v>
+        <v>76.62383270263672</v>
       </c>
       <c r="C139" t="n">
         <v>110.5899963378906</v>
@@ -3980,7 +3980,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>76.41596221923828</v>
+        <v>76.41597747802734</v>
       </c>
       <c r="C140" t="n">
         <v>110.2900009155273</v>
@@ -4009,7 +4009,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>79.82533264160156</v>
+        <v>79.82534027099609</v>
       </c>
       <c r="C141" t="n">
         <v>114.3600006103516</v>
@@ -4038,7 +4038,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>83.82498168945312</v>
+        <v>83.82496643066406</v>
       </c>
       <c r="C142" t="n">
         <v>120.0899963378906</v>
@@ -4067,7 +4067,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>82.03803253173828</v>
+        <v>82.03805541992188</v>
       </c>
       <c r="C143" t="n">
         <v>117.5299987792969</v>
@@ -4096,7 +4096,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>85.40411376953125</v>
+        <v>85.40409851074219</v>
       </c>
       <c r="C144" t="n">
         <v>121.4499969482422</v>
@@ -4125,7 +4125,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>83.78672790527344</v>
+        <v>83.78672027587891</v>
       </c>
       <c r="C145" t="n">
         <v>119.1500015258789</v>
@@ -4183,7 +4183,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>74.04360198974609</v>
+        <v>74.04361724853516</v>
       </c>
       <c r="C147" t="n">
         <v>104.4100036621094</v>
@@ -4241,7 +4241,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>80.48989868164062</v>
+        <v>80.48989105224609</v>
       </c>
       <c r="C149" t="n">
         <v>113.5</v>
@@ -4270,7 +4270,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>82.99568176269531</v>
+        <v>82.99568939208984</v>
       </c>
       <c r="C150" t="n">
         <v>116.120002746582</v>
@@ -4299,7 +4299,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>75.92691040039062</v>
+        <v>75.9268798828125</v>
       </c>
       <c r="C151" t="n">
         <v>106.2300033569336</v>
@@ -4328,7 +4328,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>85.69025421142578</v>
+        <v>85.69023895263672</v>
       </c>
       <c r="C152" t="n">
         <v>119.8899993896484</v>
@@ -4357,7 +4357,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>88.49224853515625</v>
+        <v>88.49224090576172</v>
       </c>
       <c r="C153" t="n">
         <v>122.879997253418</v>
@@ -4415,7 +4415,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>76.72494506835938</v>
+        <v>76.72496795654297</v>
       </c>
       <c r="C155" t="n">
         <v>106.5400009155273</v>
@@ -4444,7 +4444,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>83.71604156494141</v>
+        <v>83.71602630615234</v>
       </c>
       <c r="C156" t="n">
         <v>115.2900009155273</v>
@@ -4502,7 +4502,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>76.53456115722656</v>
+        <v>76.53455352783203</v>
       </c>
       <c r="C158" t="n">
         <v>105.4000015258789</v>
@@ -4531,7 +4531,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>80.72219848632812</v>
+        <v>80.72218322753906</v>
       </c>
       <c r="C159" t="n">
         <v>110.1999969482422</v>
@@ -4560,7 +4560,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>81.85025024414062</v>
+        <v>81.85024261474609</v>
       </c>
       <c r="C160" t="n">
         <v>111.7399978637695</v>
@@ -4589,7 +4589,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>77.80683135986328</v>
+        <v>77.80681610107422</v>
       </c>
       <c r="C161" t="n">
         <v>106.2200012207031</v>
@@ -4618,7 +4618,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>68.71562957763672</v>
+        <v>68.71562194824219</v>
       </c>
       <c r="C162" t="n">
         <v>92.91999816894531</v>
@@ -4647,7 +4647,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>76.36959838867188</v>
+        <v>76.36961364746094</v>
       </c>
       <c r="C163" t="n">
         <v>103.2699966430664</v>
@@ -4676,7 +4676,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>88.34973907470703</v>
+        <v>88.34972381591797</v>
       </c>
       <c r="C164" t="n">
         <v>119.4700012207031</v>
@@ -4763,7 +4763,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>85.89376831054688</v>
+        <v>85.89376068115234</v>
       </c>
       <c r="C167" t="n">
         <v>115.1699981689453</v>
@@ -4792,7 +4792,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>89.9908447265625</v>
+        <v>89.99085235595703</v>
       </c>
       <c r="C168" t="n">
         <v>119.7300033569336</v>
@@ -4821,7 +4821,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>87.98404693603516</v>
+        <v>87.98403167724609</v>
       </c>
       <c r="C169" t="n">
         <v>117.0599975585938</v>
@@ -4908,7 +4908,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>70.91161346435547</v>
+        <v>70.91159820556641</v>
       </c>
       <c r="C172" t="n">
         <v>93.41999816894531</v>
@@ -4937,7 +4937,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>71.85286712646484</v>
+        <v>71.85285949707031</v>
       </c>
       <c r="C173" t="n">
         <v>94.66000366210938</v>
@@ -4966,7 +4966,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>76.47993469238281</v>
+        <v>76.47991943359375</v>
       </c>
       <c r="C174" t="n">
         <v>99.70999908447266</v>
@@ -4995,7 +4995,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>85.27767944335938</v>
+        <v>85.27767181396484</v>
       </c>
       <c r="C175" t="n">
         <v>111.1800003051758</v>
@@ -5024,7 +5024,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>109.5003051757812</v>
+        <v>109.5002899169922</v>
       </c>
       <c r="C176" t="n">
         <v>142.7599945068359</v>
@@ -5053,7 +5053,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>126.299919128418</v>
+        <v>126.2999267578125</v>
       </c>
       <c r="C177" t="n">
         <v>163.6199951171875</v>
@@ -5111,7 +5111,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>121.2747650146484</v>
+        <v>121.274772644043</v>
       </c>
       <c r="C179" t="n">
         <v>157.1100006103516</v>
@@ -5140,7 +5140,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>132.8559112548828</v>
+        <v>132.8559265136719</v>
       </c>
       <c r="C180" t="n">
         <v>171.0700073242188</v>
@@ -5169,7 +5169,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>130.7823028564453</v>
+        <v>130.7822723388672</v>
       </c>
       <c r="C181" t="n">
         <v>168.3999938964844</v>
@@ -5198,7 +5198,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>120.3756103515625</v>
+        <v>120.3756561279297</v>
       </c>
       <c r="C182" t="n">
         <v>155</v>
@@ -5227,7 +5227,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>123.3495483398438</v>
+        <v>123.3495712280273</v>
       </c>
       <c r="C183" t="n">
         <v>157.8300018310547</v>
@@ -5256,7 +5256,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>132.8529815673828</v>
+        <v>132.85302734375</v>
       </c>
       <c r="C184" t="n">
         <v>169.9900054931641</v>
@@ -5343,7 +5343,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>163.3142852783203</v>
+        <v>163.3143157958984</v>
       </c>
       <c r="C187" t="n">
         <v>207.9700012207031</v>
@@ -5372,7 +5372,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>150.2708129882812</v>
+        <v>150.2708282470703</v>
       </c>
       <c r="C188" t="n">
         <v>191.3600006103516</v>
@@ -5401,7 +5401,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>154.4356994628906</v>
+        <v>154.4357147216797</v>
       </c>
       <c r="C189" t="n">
         <v>195.6300048828125</v>
@@ -5488,7 +5488,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>157.3724517822266</v>
+        <v>157.3724060058594</v>
       </c>
       <c r="C192" t="n">
         <v>198.3699951171875</v>
@@ -5517,7 +5517,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>170.0419006347656</v>
+        <v>170.0418853759766</v>
       </c>
       <c r="C193" t="n">
         <v>214.3399963378906</v>
@@ -5546,7 +5546,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>160.4188079833984</v>
+        <v>160.4188385009766</v>
       </c>
       <c r="C194" t="n">
         <v>202.2100067138672</v>
@@ -5662,7 +5662,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>146.88427734375</v>
+        <v>146.8842926025391</v>
       </c>
       <c r="C198" t="n">
         <v>182.25</v>
@@ -5691,7 +5691,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>147.1180114746094</v>
+        <v>147.1179656982422</v>
       </c>
       <c r="C199" t="n">
         <v>182.5399932861328</v>
@@ -5720,7 +5720,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>157.0715179443359</v>
+        <v>157.0714874267578</v>
       </c>
       <c r="C200" t="n">
         <v>194.8899993896484</v>
@@ -5749,7 +5749,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>157.9395446777344</v>
+        <v>157.9395599365234</v>
       </c>
       <c r="C201" t="n">
         <v>194.5099945068359</v>
@@ -5778,7 +5778,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>131.1683349609375</v>
+        <v>131.1683654785156</v>
       </c>
       <c r="C202" t="n">
         <v>161.5399932861328</v>
@@ -5807,7 +5807,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>136.2270355224609</v>
+        <v>136.2270050048828</v>
       </c>
       <c r="C203" t="n">
         <v>167.7700042724609</v>
@@ -5836,7 +5836,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>155.4993896484375</v>
+        <v>155.4994049072266</v>
       </c>
       <c r="C204" t="n">
         <v>189.7299957275391</v>
@@ -5865,7 +5865,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>142.4762115478516</v>
+        <v>142.4762573242188</v>
       </c>
       <c r="C205" t="n">
         <v>173.8399963378906</v>
@@ -5894,7 +5894,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>151.811279296875</v>
+        <v>151.8112487792969</v>
       </c>
       <c r="C206" t="n">
         <v>185.2299957275391</v>
@@ -5923,7 +5923,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>150.8829650878906</v>
+        <v>150.8829498291016</v>
       </c>
       <c r="C207" t="n">
         <v>182.4900054931641</v>
@@ -5952,7 +5952,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>160.3911590576172</v>
+        <v>160.3911743164062</v>
       </c>
       <c r="C208" t="n">
         <v>193.9900054931641</v>
@@ -6039,7 +6039,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>149.6280517578125</v>
+        <v>149.6280822753906</v>
       </c>
       <c r="C211" t="n">
         <v>179.25</v>
@@ -6068,7 +6068,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>156.2058563232422</v>
+        <v>156.2058258056641</v>
       </c>
       <c r="C212" t="n">
         <v>187.1300048828125</v>
@@ -6097,7 +6097,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>142.6872711181641</v>
+        <v>142.6872863769531</v>
       </c>
       <c r="C213" t="n">
         <v>169.3999938964844</v>
@@ -6126,7 +6126,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>131.2908325195312</v>
+        <v>131.2908477783203</v>
       </c>
       <c r="C214" t="n">
         <v>155.8699951171875</v>
@@ -6155,7 +6155,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>118.9762878417969</v>
+        <v>118.9762725830078</v>
       </c>
       <c r="C215" t="n">
         <v>141.25</v>
@@ -6213,7 +6213,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>133.9873809814453</v>
+        <v>133.9873504638672</v>
       </c>
       <c r="C217" t="n">
         <v>157.2299957275391</v>
@@ -6242,7 +6242,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>120.9235153198242</v>
+        <v>120.9235382080078</v>
       </c>
       <c r="C218" t="n">
         <v>141.8999938964844</v>
@@ -6271,7 +6271,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>127.7601776123047</v>
+        <v>127.7602081298828</v>
       </c>
       <c r="C219" t="n">
         <v>148.2599945068359</v>
@@ -6300,7 +6300,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>128.0790557861328</v>
+        <v>128.0790405273438</v>
       </c>
       <c r="C220" t="n">
         <v>148.6300048828125</v>
@@ -6329,7 +6329,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>127.0880508422852</v>
+        <v>127.0880661010742</v>
       </c>
       <c r="C221" t="n">
         <v>147.4799957275391</v>
@@ -6358,7 +6358,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>121.0529403686523</v>
+        <v>121.0529327392578</v>
       </c>
       <c r="C222" t="n">
         <v>138.9299926757812</v>
@@ -6387,7 +6387,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>119.2406005859375</v>
+        <v>119.240608215332</v>
       </c>
       <c r="C223" t="n">
         <v>136.8500061035156</v>
@@ -6416,7 +6416,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>113.5943984985352</v>
+        <v>113.5944061279297</v>
       </c>
       <c r="C224" t="n">
         <v>130.3699951171875</v>
@@ -6445,7 +6445,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>113.4347457885742</v>
+        <v>113.4347381591797</v>
       </c>
       <c r="C225" t="n">
         <v>128.5500030517578</v>
@@ -6474,7 +6474,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>120.3087692260742</v>
+        <v>120.3087539672852</v>
       </c>
       <c r="C226" t="n">
         <v>136.3399963378906</v>
@@ -6503,7 +6503,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>118.2968673706055</v>
+        <v>118.2968521118164</v>
       </c>
       <c r="C227" t="n">
         <v>134.0599975585938</v>
@@ -6590,7 +6590,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>102.0390930175781</v>
+        <v>102.0391006469727</v>
       </c>
       <c r="C230" t="n">
         <v>114.2300033569336</v>
@@ -6619,7 +6619,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>107.8486862182617</v>
+        <v>107.8486938476562</v>
       </c>
       <c r="C231" t="n">
         <v>119.0299987792969</v>
@@ -6648,7 +6648,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>99.65789031982422</v>
+        <v>99.65788269042969</v>
       </c>
       <c r="C232" t="n">
         <v>109.9899978637695</v>
@@ -6735,7 +6735,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>92.96273803710938</v>
+        <v>92.96274566650391</v>
       </c>
       <c r="C235" t="n">
         <v>100.9400024414062</v>
@@ -6764,7 +6764,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>79.35080718994141</v>
+        <v>79.35079956054688</v>
       </c>
       <c r="C236" t="n">
         <v>86.16000366210938</v>
@@ -6793,7 +6793,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>82.05047607421875</v>
+        <v>82.05046844482422</v>
       </c>
       <c r="C237" t="n">
         <v>87.44000244140625</v>
@@ -6822,7 +6822,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>78.3814697265625</v>
+        <v>78.38147735595703</v>
       </c>
       <c r="C238" t="n">
         <v>83.52999877929688</v>
@@ -6851,7 +6851,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>90.47696685791016</v>
+        <v>90.47695922851562</v>
       </c>
       <c r="C239" t="n">
         <v>96.41999816894531</v>
@@ -6880,7 +6880,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>91.4483642578125</v>
+        <v>91.44837188720703</v>
       </c>
       <c r="C240" t="n">
         <v>95.79000091552734</v>
@@ -6909,7 +6909,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>94.69427490234375</v>
+        <v>94.69426727294922</v>
       </c>
       <c r="C241" t="n">
         <v>99.19000244140625</v>
@@ -6938,7 +6938,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>101.405632019043</v>
+        <v>101.4056396484375</v>
       </c>
       <c r="C242" t="n">
         <v>106.2200012207031</v>
